--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260929.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.33%</t>
+          <t>26.63%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.14%</t>
+          <t>8.20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.59%</t>
+          <t>7.49%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.16%</t>
+          <t>7.28%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.00%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.52%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>18,455</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,455</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
